--- a/docs/tests/test-specification.xlsx
+++ b/docs/tests/test-specification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\java00\Desktop\portfolio\inventory-app\docs\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52AB2CE-E4C6-445D-ADA8-3C98F6D4B44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F68A002-40DE-4F6D-A5E1-99A9A3BC4B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧・接続" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="125">
   <si>
     <t>在庫管理Webアプリ｜一覧・接続 テスト仕様書兼実施記録</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>DB接続</t>
-  </si>
-  <si>
-    <t>テストDBへ接続した状態で /con_check を開く</t>
   </si>
   <si>
     <t>「接続成功！」と表示される</t>
@@ -414,6 +411,13 @@
   <si>
     <t>実施方法：各ケースでDBを指定状態に戻す → 操作する → 期待結果と比較 → 判定・実施日・備考を記入</t>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>DBへ接続した状態で /con_check を開く</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -1036,14 +1040,14 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="str">
         <f>COUNTIF(E8:E11,"OK")&amp;" / "&amp;COUNTA(A8:A11)&amp;" 件 合格"</f>
-        <v>0 / 4 件 合格</v>
+        <v>4 / 4 件 合格</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1054,7 +1058,7 @@
     </row>
     <row r="5" spans="1:7" ht="25.05" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1105,72 +1109,80 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="7"/>
+        <v>124</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46324</v>
+      </c>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="49.05" customHeight="1">
       <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="8"/>
+        <v>124</v>
+      </c>
+      <c r="F9" s="8">
+        <v>46324</v>
+      </c>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="49.05" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="7"/>
+        <v>124</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46324</v>
+      </c>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="49.05" customHeight="1">
       <c r="A11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="8"/>
+        <v>124</v>
+      </c>
+      <c r="F11" s="8">
+        <v>46324</v>
+      </c>
       <c r="G11" s="3"/>
     </row>
   </sheetData>
@@ -1226,7 +1238,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1250,7 +1262,7 @@
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="str">
@@ -1262,7 +1274,7 @@
     </row>
     <row r="4" spans="1:7" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1318,228 +1330,228 @@
     </row>
     <row r="8" spans="1:7" ht="49.05" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="49.05" customHeight="1">
       <c r="A9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="49.05" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="49.05" customHeight="1">
       <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="49.05" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="49.05" customHeight="1">
       <c r="A13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" ht="49.05" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="49.05" customHeight="1">
       <c r="A15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E15" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" ht="49.05" customHeight="1">
       <c r="A16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" ht="49.05" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" ht="49.05" customHeight="1">
       <c r="A18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="E18" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" ht="49.05" customHeight="1">
       <c r="A19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="3"/>
@@ -1597,7 +1609,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1621,7 +1633,7 @@
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="str">
@@ -1633,7 +1645,7 @@
     </row>
     <row r="4" spans="1:7" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1689,133 +1701,133 @@
     </row>
     <row r="8" spans="1:7" ht="49.05" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="49.05" customHeight="1">
       <c r="A9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="49.05" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="49.05" customHeight="1">
       <c r="A11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="49.05" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="E12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="49.05" customHeight="1">
       <c r="A13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E13" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" ht="49.05" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="2"/>
@@ -1873,7 +1885,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1897,7 +1909,7 @@
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="str">
@@ -1909,7 +1921,7 @@
     </row>
     <row r="4" spans="1:7" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1965,76 +1977,76 @@
     </row>
     <row r="8" spans="1:7" ht="49.05" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="49.05" customHeight="1">
       <c r="A9" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="49.05" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="49.05" customHeight="1">
       <c r="A11" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="3"/>
